--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7530,6 +7530,27 @@
         <v>395.5</v>
       </c>
       <c r="E338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>323.49</v>
+      </c>
+      <c r="C339" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="D339" t="n">
+        <v>396.61</v>
+      </c>
+      <c r="E339" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7546,7 +7567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B379"/>
+  <dimension ref="A1:B380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11339,6 +11360,16 @@
       </c>
       <c r="B379" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>
@@ -11507,28 +11538,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.000208666743894427</v>
+        <v>-0.009933649352340933</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52840513578667e-08</v>
+        <v>3.469984088810829e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.663904539265818</v>
+        <v>9.677279229201993</v>
       </c>
       <c r="N2" t="n">
-        <v>152.1460513026327</v>
+        <v>152.4446110125311</v>
       </c>
       <c r="O2" t="n">
-        <v>12.33474974625074</v>
+        <v>12.34684619700639</v>
       </c>
       <c r="P2" t="n">
-        <v>339.4807565099146</v>
+        <v>339.5818640181198</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11585,28 +11616,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0696370418237801</v>
+        <v>0.06189236518976413</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001918027110268006</v>
+        <v>0.001520618440934429</v>
       </c>
       <c r="M3" t="n">
-        <v>9.136465565300336</v>
+        <v>9.143509949366498</v>
       </c>
       <c r="N3" t="n">
-        <v>134.7673845258892</v>
+        <v>134.8434903525211</v>
       </c>
       <c r="O3" t="n">
-        <v>11.60893554663343</v>
+        <v>11.61221298256801</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0661323678081</v>
+        <v>338.1466512733782</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11663,28 +11694,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3926884124412833</v>
+        <v>0.3915018404815992</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1288198521711598</v>
+        <v>0.1288755125736238</v>
       </c>
       <c r="M4" t="n">
-        <v>5.795531763303643</v>
+        <v>5.783226681063462</v>
       </c>
       <c r="N4" t="n">
-        <v>55.69472295342275</v>
+        <v>55.54109158815933</v>
       </c>
       <c r="O4" t="n">
-        <v>7.462889718696287</v>
+        <v>7.452589589408459</v>
       </c>
       <c r="P4" t="n">
-        <v>388.2378046954684</v>
+        <v>388.2501411015043</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11722,7 +11753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20851,6 +20882,33 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-35.839221126917074,174.5793557327156</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-35.83995793689805,174.57952395251516</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-35.84050519177023,174.58050770377247</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7551,6 +7551,27 @@
         <v>396.61</v>
       </c>
       <c r="E339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>326.31</v>
+      </c>
+      <c r="C340" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="D340" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="E340" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7567,7 +7588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B380"/>
+  <dimension ref="A1:B381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11370,6 +11391,16 @@
       </c>
       <c r="B380" t="n">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -11538,28 +11569,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.009933649352340933</v>
+        <v>-0.01783192560558554</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>3.469984088810829e-05</v>
+        <v>0.0001122026987911973</v>
       </c>
       <c r="M2" t="n">
-        <v>9.677279229201993</v>
+        <v>9.682424248410632</v>
       </c>
       <c r="N2" t="n">
-        <v>152.4446110125311</v>
+        <v>152.4890900382877</v>
       </c>
       <c r="O2" t="n">
-        <v>12.34684619700639</v>
+        <v>12.34864729588985</v>
       </c>
       <c r="P2" t="n">
-        <v>339.5818640181198</v>
+        <v>339.6642827123349</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11616,28 +11647,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06189236518976413</v>
+        <v>0.05502213767978928</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001520618440934429</v>
+        <v>0.001206956593154174</v>
       </c>
       <c r="M3" t="n">
-        <v>9.143509949366498</v>
+        <v>9.146877499446489</v>
       </c>
       <c r="N3" t="n">
-        <v>134.8434903525211</v>
+        <v>134.8196192575084</v>
       </c>
       <c r="O3" t="n">
-        <v>11.61221298256801</v>
+        <v>11.61118509272453</v>
       </c>
       <c r="P3" t="n">
-        <v>338.1466512733782</v>
+        <v>338.2183422553315</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11694,28 +11725,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3915018404815992</v>
+        <v>0.3904956342064733</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1288755125736238</v>
+        <v>0.1290416135128197</v>
       </c>
       <c r="M4" t="n">
-        <v>5.783226681063462</v>
+        <v>5.770242810399994</v>
       </c>
       <c r="N4" t="n">
-        <v>55.54109158815933</v>
+        <v>55.38527374049391</v>
       </c>
       <c r="O4" t="n">
-        <v>7.452589589408459</v>
+        <v>7.442128307177585</v>
       </c>
       <c r="P4" t="n">
-        <v>388.2501411015043</v>
+        <v>388.2606408871092</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11753,7 +11784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20909,6 +20940,33 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-35.8392173718101,174.57938660807486</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-35.83995544792341,174.5795380154832</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-35.8405044195914,174.5805110019449</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7574,6 +7574,27 @@
       <c r="E340" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>337.72</v>
+      </c>
+      <c r="C341" t="n">
+        <v>333.19</v>
+      </c>
+      <c r="D341" t="n">
+        <v>399.7</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B381"/>
+  <dimension ref="A1:B382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11401,6 +11422,16 @@
       </c>
       <c r="B381" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -11569,28 +11600,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01783192560558554</v>
+        <v>-0.01872770447288086</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001122026987911973</v>
+        <v>0.0001246053390417945</v>
       </c>
       <c r="M2" t="n">
-        <v>9.682424248410632</v>
+        <v>9.657699450941493</v>
       </c>
       <c r="N2" t="n">
-        <v>152.4890900382877</v>
+        <v>152.0468802543696</v>
       </c>
       <c r="O2" t="n">
-        <v>12.34864729588985</v>
+        <v>12.33072910473544</v>
       </c>
       <c r="P2" t="n">
-        <v>339.6642827123349</v>
+        <v>339.6736895829925</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11647,28 +11678,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05502213767978928</v>
+        <v>0.05106882372501695</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001206956593154174</v>
+        <v>0.0010461331932895</v>
       </c>
       <c r="M3" t="n">
-        <v>9.146877499446489</v>
+        <v>9.137222937982765</v>
       </c>
       <c r="N3" t="n">
-        <v>134.8196192575084</v>
+        <v>134.5455530726535</v>
       </c>
       <c r="O3" t="n">
-        <v>11.61118509272453</v>
+        <v>11.59937727089923</v>
       </c>
       <c r="P3" t="n">
-        <v>338.2183422553315</v>
+        <v>338.259857314906</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11725,28 +11756,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3904956342064733</v>
+        <v>0.3911551280790937</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1290416135128197</v>
+        <v>0.1301905541944685</v>
       </c>
       <c r="M4" t="n">
-        <v>5.770242810399994</v>
+        <v>5.756951260104025</v>
       </c>
       <c r="N4" t="n">
-        <v>55.38527374049391</v>
+        <v>55.22578388487173</v>
       </c>
       <c r="O4" t="n">
-        <v>7.442128307177585</v>
+        <v>7.431405242945087</v>
       </c>
       <c r="P4" t="n">
-        <v>388.2606408871092</v>
+        <v>388.253715323462</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11784,7 +11815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20967,6 +20998,33 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-35.839202178194164,174.57951153281124</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-35.83994641101721,174.57958907486702</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-35.84049749488691,174.58054057910124</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -7609,7 +7609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B382"/>
+  <dimension ref="A1:B383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11432,6 +11432,16 @@
       </c>
       <c r="B382" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7595,6 +7595,69 @@
       <c r="E341" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="C342" t="n">
+        <v>331.87</v>
+      </c>
+      <c r="D342" t="n">
+        <v>399.37</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="C343" t="n">
+        <v>328.38</v>
+      </c>
+      <c r="D343" t="n">
+        <v>394.66</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>327.22</v>
+      </c>
+      <c r="C344" t="n">
+        <v>326.14</v>
+      </c>
+      <c r="D344" t="n">
+        <v>394.4</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B383"/>
+  <dimension ref="A1:B386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11442,6 +11505,36 @@
       </c>
       <c r="B383" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -11610,28 +11703,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01872770447288086</v>
+        <v>-0.03276660213112854</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001246053390417945</v>
+        <v>0.0003877317249234569</v>
       </c>
       <c r="M2" t="n">
-        <v>9.657699450941493</v>
+        <v>9.630779724464263</v>
       </c>
       <c r="N2" t="n">
-        <v>152.0468802543696</v>
+        <v>151.3382643588643</v>
       </c>
       <c r="O2" t="n">
-        <v>12.33072910473544</v>
+        <v>12.30196180935643</v>
       </c>
       <c r="P2" t="n">
-        <v>339.6736895829925</v>
+        <v>339.8222086592555</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11688,28 +11781,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05106882372501695</v>
+        <v>0.03153526112751494</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0010461331932895</v>
+        <v>0.00040435442678044</v>
       </c>
       <c r="M3" t="n">
-        <v>9.137222937982765</v>
+        <v>9.143030210752991</v>
       </c>
       <c r="N3" t="n">
-        <v>134.5455530726535</v>
+        <v>134.4128252268545</v>
       </c>
       <c r="O3" t="n">
-        <v>11.59937727089923</v>
+        <v>11.59365452421515</v>
       </c>
       <c r="P3" t="n">
-        <v>338.259857314906</v>
+        <v>338.4664699422955</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11766,28 +11859,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3911551280790937</v>
+        <v>0.3865418782479456</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1301905541944685</v>
+        <v>0.1296422309822033</v>
       </c>
       <c r="M4" t="n">
-        <v>5.756951260104025</v>
+        <v>5.729254259107377</v>
       </c>
       <c r="N4" t="n">
-        <v>55.22578388487173</v>
+        <v>54.84412505554118</v>
       </c>
       <c r="O4" t="n">
-        <v>7.431405242945087</v>
+        <v>7.405681943990113</v>
       </c>
       <c r="P4" t="n">
-        <v>388.253715323462</v>
+        <v>388.302531715489</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11825,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21035,6 +21128,87 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-35.839204734885264,174.57949051129924</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-35.839948938289744,174.57957479554906</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-35.840498316884585,174.5805370681441</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-35.83921090022431,174.57943981879285</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-35.83995562023709,174.57953704189316</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-35.840510049022136,174.58048695720234</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.83921616005404,174.57939657139931</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.83995990893065,174.57951281031674</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.84051069665545,174.5804841909928</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7658,6 +7658,27 @@
       <c r="E344" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>323.68</v>
+      </c>
+      <c r="C345" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="D345" t="n">
+        <v>395.52</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11535,6 +11556,16 @@
       </c>
       <c r="B386" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -11703,28 +11734,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03276660213112854</v>
+        <v>-0.04192409319418219</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003877317249234569</v>
+        <v>0.0006361109971547707</v>
       </c>
       <c r="M2" t="n">
-        <v>9.630779724464263</v>
+        <v>9.640150895790031</v>
       </c>
       <c r="N2" t="n">
-        <v>151.3382643588643</v>
+        <v>151.5689467196876</v>
       </c>
       <c r="O2" t="n">
-        <v>12.30196180935643</v>
+        <v>12.31133407554549</v>
       </c>
       <c r="P2" t="n">
-        <v>339.8222086592555</v>
+        <v>339.9193975271039</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11781,28 +11812,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03153526112751494</v>
+        <v>0.02213974099388778</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00040435442678044</v>
+        <v>0.0001996606755346741</v>
       </c>
       <c r="M3" t="n">
-        <v>9.143030210752991</v>
+        <v>9.158575746539123</v>
       </c>
       <c r="N3" t="n">
-        <v>134.4128252268545</v>
+        <v>134.7280251089585</v>
       </c>
       <c r="O3" t="n">
-        <v>11.59365452421515</v>
+        <v>11.6072402020876</v>
       </c>
       <c r="P3" t="n">
-        <v>338.4664699422955</v>
+        <v>338.566185023462</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11859,28 +11890,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3865418782479456</v>
+        <v>0.3846627912761224</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1296422309822033</v>
+        <v>0.1292565910999922</v>
       </c>
       <c r="M4" t="n">
-        <v>5.729254259107377</v>
+        <v>5.720329714961717</v>
       </c>
       <c r="N4" t="n">
-        <v>54.84412505554118</v>
+        <v>54.71293134044836</v>
       </c>
       <c r="O4" t="n">
-        <v>7.405681943990113</v>
+        <v>7.396819001465992</v>
       </c>
       <c r="P4" t="n">
-        <v>388.302531715489</v>
+        <v>388.322474550718</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11918,7 +11949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21209,6 +21240,33 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.83922087391366,174.5793578129704</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.83996467626738,174.57948587432003</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.84050790684993,174.58049610697205</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
